--- a/Assets/Resources/Excel/Record.xlsx
+++ b/Assets/Resources/Excel/Record.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C50D8701-310B-4BB5-9382-8F365AFE95A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92C90248-05E6-40F9-B28B-EC1778BC0CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="69">
   <si>
     <t>CharacterTID</t>
   </si>
@@ -42,6 +42,9 @@
     <t>CharacterName</t>
   </si>
   <si>
+    <t>RecordName</t>
+  </si>
+  <si>
     <t>RequiredLevel</t>
   </si>
   <si>
@@ -57,6 +60,9 @@
     <t>Yuan</t>
   </si>
   <si>
+    <t>약속</t>
+  </si>
+  <si>
     <t>유안</t>
   </si>
   <si>
@@ -102,6 +108,9 @@
     <t>...네. 들리네요.</t>
   </si>
   <si>
+    <t>닻</t>
+  </si>
+  <si>
     <t>유안, 몸은 괜찮아? 담요 가져올까? 이번 출격은 평소보다 오래 걸렸으니까.</t>
   </si>
   <si>
@@ -138,6 +147,9 @@
     <t>고마워요. ...언젠가는 저도 제 힘으로 돌아올 수 있으면 좋겠어요. 관제사님 목소리 없이도.</t>
   </si>
   <si>
+    <t>임계점</t>
+  </si>
+  <si>
     <t>유안. 이번 출격은 중단해야 해. 침식 중심부의 위험 지수가 임계점을 넘었어.</t>
   </si>
   <si>
@@ -190,6 +202,9 @@
   </si>
   <si>
     <t>다녀올게요, 관제사님.</t>
+  </si>
+  <si>
+    <t>두 번째 첫 만남</t>
   </si>
   <si>
     <t>관제사님. 기록... 봤어요.</t>
@@ -577,16 +592,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="161.75" customWidth="1"/>
+    <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="161.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,1105 +621,1273 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>101101</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>101102</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>101103</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>101104</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
       <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>101105</v>
       </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
       <c r="F6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>101106</v>
       </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
       <c r="F7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>101107</v>
       </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
       <c r="F8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>101108</v>
       </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
       <c r="F9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>101109</v>
       </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
       <c r="F10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>101110</v>
       </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
       <c r="F11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
         <v>1</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>101111</v>
       </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
       <c r="F12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>101112</v>
       </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
       <c r="F13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
         <v>1</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>101113</v>
       </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
       <c r="F14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>101201</v>
       </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
       <c r="F15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>101202</v>
       </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
       <c r="F16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>101203</v>
       </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
       <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18">
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>101204</v>
       </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
       <c r="F18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>101205</v>
       </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
       <c r="F19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
         <v>2</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>101206</v>
       </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
       <c r="F20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>101207</v>
       </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
       <c r="F21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
         <v>2</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>101208</v>
       </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
       <c r="F22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23">
         <v>2</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>101209</v>
       </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
       <c r="F23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24">
         <v>2</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>101210</v>
       </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
       <c r="F24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25">
         <v>2</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>101211</v>
       </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
       <c r="F25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
         <v>2</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>101212</v>
       </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
       <c r="F26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27">
         <v>3</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>101301</v>
       </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
       <c r="F27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>101302</v>
       </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
       <c r="F28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29">
         <v>3</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>101303</v>
       </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
       <c r="F29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30">
         <v>3</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>101304</v>
       </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
       <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>101</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31">
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>101305</v>
       </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
       <c r="F31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32">
         <v>3</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>101306</v>
       </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
       <c r="F32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33">
         <v>3</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>101307</v>
       </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
       <c r="F33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34">
         <v>3</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>101308</v>
       </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
       <c r="F34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35">
         <v>3</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>101309</v>
       </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
       <c r="F35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36">
         <v>3</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>101310</v>
       </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
       <c r="F36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37">
         <v>3</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>101311</v>
       </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
       <c r="F37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38">
         <v>3</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>101312</v>
       </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
       <c r="F38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39">
         <v>3</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>101313</v>
       </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
       <c r="F39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40">
         <v>3</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>101314</v>
       </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
       <c r="F40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41">
         <v>3</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>101315</v>
       </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
       <c r="F41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42">
         <v>3</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>101316</v>
       </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
       <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43">
         <v>3</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>101317</v>
       </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
       <c r="F43" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44">
         <v>3</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>101318</v>
       </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
       <c r="F44" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45">
         <v>4</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>101401</v>
       </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
       <c r="F45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46">
         <v>4</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>101402</v>
       </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
       <c r="F46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47">
         <v>4</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>101403</v>
       </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
       <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48">
         <v>4</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>101404</v>
       </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
       <c r="F48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49">
         <v>4</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>101405</v>
       </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
       <c r="F49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>101</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>101</v>
-      </c>
-      <c r="B50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50">
+      <c r="D50">
         <v>4</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>101406</v>
       </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
       <c r="F50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51">
         <v>4</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>101407</v>
       </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
       <c r="F51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52">
         <v>4</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>101408</v>
       </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
       <c r="F52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53">
         <v>4</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>101409</v>
       </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
       <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54">
         <v>4</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>101410</v>
       </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
       <c r="F54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55">
         <v>4</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>101411</v>
       </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
       <c r="F55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56">
         <v>4</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>101412</v>
       </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
       <c r="F56" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Excel/Record.xlsx
+++ b/Assets/Resources/Excel/Record.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30317"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92C90248-05E6-40F9-B28B-EC1778BC0CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E63C9E89-286D-4CD5-BAF6-5C7577F810FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="79">
   <si>
     <t>CharacterTID</t>
   </si>
@@ -45,6 +45,12 @@
     <t>RecordName</t>
   </si>
   <si>
+    <t>MainImage</t>
+  </si>
+  <si>
+    <t>BackgroundImage</t>
+  </si>
+  <si>
     <t>RequiredLevel</t>
   </si>
   <si>
@@ -63,6 +69,12 @@
     <t>약속</t>
   </si>
   <si>
+    <t>Record_Yuan_01</t>
+  </si>
+  <si>
+    <t>Record_Background_Yuan_01</t>
+  </si>
+  <si>
     <t>유안</t>
   </si>
   <si>
@@ -111,6 +123,12 @@
     <t>닻</t>
   </si>
   <si>
+    <t>Record_Yuan_02</t>
+  </si>
+  <si>
+    <t>Record_Background_Yuan_02</t>
+  </si>
+  <si>
     <t>유안, 몸은 괜찮아? 담요 가져올까? 이번 출격은 평소보다 오래 걸렸으니까.</t>
   </si>
   <si>
@@ -150,6 +168,12 @@
     <t>임계점</t>
   </si>
   <si>
+    <t>Record_Yuan_03</t>
+  </si>
+  <si>
+    <t>Record_Background_Yuan_03</t>
+  </si>
+  <si>
     <t>유안. 이번 출격은 중단해야 해. 침식 중심부의 위험 지수가 임계점을 넘었어.</t>
   </si>
   <si>
@@ -205,6 +229,12 @@
   </si>
   <si>
     <t>두 번째 첫 만남</t>
+  </si>
+  <si>
+    <t>Record_Yuan_04</t>
+  </si>
+  <si>
+    <t>Record_Background_Yuan_04</t>
   </si>
   <si>
     <t>관제사님. 기록... 봤어요.</t>
@@ -592,17 +622,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="161.75" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="161.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,1270 +656,1606 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>101101</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>101102</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>101103</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>101104</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>101</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>101105</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>101106</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>101107</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>101108</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>101109</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>101110</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>101</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12">
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>101111</v>
       </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>101112</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="G13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>101</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14">
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>101113</v>
       </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>101201</v>
       </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>101202</v>
       </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>101203</v>
       </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>101204</v>
       </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19">
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19">
         <v>2</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>101205</v>
       </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20">
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>101206</v>
       </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>101</v>
-      </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21">
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>101207</v>
       </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>101208</v>
       </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>101209</v>
       </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>101210</v>
       </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25">
         <v>2</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>101211</v>
       </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26">
         <v>2</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>101212</v>
       </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27">
+        <v>43</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27">
         <v>3</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>101301</v>
       </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28">
         <v>3</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>101302</v>
       </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29">
         <v>3</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>101303</v>
       </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30">
         <v>3</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>101304</v>
       </c>
-      <c r="F30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>101305</v>
       </c>
-      <c r="F31" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <v>101306</v>
       </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33">
         <v>3</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>101307</v>
       </c>
-      <c r="F33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>101</v>
-      </c>
-      <c r="B34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34">
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34">
         <v>3</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>101308</v>
       </c>
-      <c r="F34" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>101</v>
-      </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35">
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>101309</v>
       </c>
-      <c r="F35" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36">
         <v>3</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>101310</v>
       </c>
-      <c r="F36" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37">
+        <v>43</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37">
         <v>3</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>101311</v>
       </c>
-      <c r="F37" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38">
         <v>3</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>101312</v>
       </c>
-      <c r="F38" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39">
+        <v>43</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>101313</v>
       </c>
-      <c r="F39" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40">
         <v>3</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>101314</v>
       </c>
-      <c r="F40" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41">
         <v>3</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>101315</v>
       </c>
-      <c r="F41" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42">
         <v>3</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>101316</v>
       </c>
-      <c r="F42" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43">
         <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43">
         <v>3</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>101317</v>
       </c>
-      <c r="F43" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44">
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44">
         <v>3</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>101318</v>
       </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45">
+        <v>64</v>
+      </c>
+      <c r="D45" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45">
         <v>4</v>
       </c>
-      <c r="E45">
+      <c r="G45">
         <v>101401</v>
       </c>
-      <c r="F45" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46">
         <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46">
+        <v>64</v>
+      </c>
+      <c r="D46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46">
         <v>4</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>101402</v>
       </c>
-      <c r="F46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47">
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47">
+        <v>64</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" t="s">
+        <v>66</v>
+      </c>
+      <c r="F47">
         <v>4</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>101403</v>
       </c>
-      <c r="F47" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48">
         <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" t="s">
+        <v>66</v>
+      </c>
+      <c r="F48">
         <v>4</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>101404</v>
       </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49">
+        <v>64</v>
+      </c>
+      <c r="D49" t="s">
+        <v>65</v>
+      </c>
+      <c r="E49" t="s">
+        <v>66</v>
+      </c>
+      <c r="F49">
         <v>4</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>101405</v>
       </c>
-      <c r="F49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50">
+        <v>64</v>
+      </c>
+      <c r="D50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F50">
         <v>4</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>101406</v>
       </c>
-      <c r="F50" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51">
+        <v>64</v>
+      </c>
+      <c r="D51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51">
         <v>4</v>
       </c>
-      <c r="E51">
+      <c r="G51">
         <v>101407</v>
       </c>
-      <c r="F51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52">
+        <v>64</v>
+      </c>
+      <c r="D52" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52">
         <v>4</v>
       </c>
-      <c r="E52">
+      <c r="G52">
         <v>101408</v>
       </c>
-      <c r="F52" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>101</v>
-      </c>
-      <c r="B53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53">
         <v>4</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <v>101409</v>
       </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>101</v>
-      </c>
-      <c r="B54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54">
+      <c r="E54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54">
         <v>4</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>101410</v>
       </c>
-      <c r="F54" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>101</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>101</v>
-      </c>
-      <c r="B55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55">
+      <c r="F55">
         <v>4</v>
       </c>
-      <c r="E55">
+      <c r="G55">
         <v>101411</v>
       </c>
-      <c r="F55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56">
         <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56">
+        <v>64</v>
+      </c>
+      <c r="D56" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56">
         <v>4</v>
       </c>
-      <c r="E56">
+      <c r="G56">
         <v>101412</v>
       </c>
-      <c r="F56" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" t="s">
-        <v>68</v>
+      <c r="H56" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
